--- a/artfynd/A 878-2024 artfynd.xlsx
+++ b/artfynd/A 878-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 878-2024 artfynd.xlsx
+++ b/artfynd/A 878-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>81354161</v>
       </c>
       <c r="B2" t="n">
-        <v>107505</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81354160</v>
+        <v>80680037</v>
       </c>
       <c r="B3" t="n">
-        <v>107630</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,6 +825,10 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västra Eneby socken, Fridhem, 500 m S, Ög</t>
@@ -881,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Leg. Tommy Nilsson {RUB/RN: 642284,149176 Lokal: Ög, V. Eneby sn; 500 m S Fridhem. Biotop: Näringsrik granskogssluttning. Datum: 030619 Leg. Tommy Nilsson Nr. 713 conf. T. Tyler 2004}</t>
+          <t>Leg. Tommy Nilsson {Hieracium macradenium, Ög, V. Eneby sn; 500 m S Fridhem. Näringsrik granskogssluttning. RN, 642284, 149176. Conf. T. Tyler 2004. Tommy Nilsson}</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,12 +895,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
+          <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>713, S-A15117-88</t>
+          <t>1815939</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,11 +914,7 @@
           <t>Via Anders Svenson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Äldre fynd i Östergötlands flora</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 878-2024 artfynd.xlsx
+++ b/artfynd/A 878-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81354161</t>
         </is>
       </c>
     </row>
@@ -915,8 +925,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80680037</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>